--- a/servers/maze_main_server_dev/conf.d/data/maze_item_attr_v8【迷宫-道具-道具id对应属性id】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_item_attr_v8【迷宫-道具-道具id对应属性id】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9500094-B4A5-4BA4-B76B-62ECB8CD9E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E6D28-BBFA-4C14-827A-76F2D3288F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4BF97ACB-F0BA-43EF-B194-721BB819C92D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4BF97ACB-F0BA-43EF-B194-721BB819C92D}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_item_attr_v8" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -498,46 +496,53 @@
       <c r="A6" s="1">
         <v>48300002</v>
       </c>
+      <c r="B6">
+        <v>3540100</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>48300003</v>
       </c>
+      <c r="B7">
+        <v>3540300</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>48300004</v>
       </c>
+      <c r="B8">
+        <v>3540500</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>48300005</v>
       </c>
+      <c r="B9">
+        <v>3540700</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>48300006</v>
       </c>
+      <c r="B10">
+        <v>3541100</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>48300007</v>
-      </c>
+      <c r="A11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>48300008</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>48300009</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>48300010</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
